--- a/資料/説明(パッシブ・スキル)/黒い砂漠M_説明_DS.xlsx
+++ b/資料/説明(パッシブ・スキル)/黒い砂漠M_説明_DS.xlsx
@@ -2,27 +2,28 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="パッシブ(①)" sheetId="1" r:id="R39dd3060370f49b8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="パッシブ(②)" sheetId="2" r:id="R4b79aeee4b2a4a59"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(０)" sheetId="3" r:id="Rd99d7d6fc6bf4385"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(1)" sheetId="4" r:id="R3810d1e0be26470e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(2)" sheetId="5" r:id="Ra242d326276c429d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(3)" sheetId="6" r:id="R710adec29c524e01"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(4)" sheetId="7" r:id="R9295c05d5fe44e29"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(5)" sheetId="8" r:id="Rbe815c8947624366"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(6)" sheetId="9" r:id="Rcb3e63e7e90247fe"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(7)" sheetId="10" r:id="Rb14a1b45e11d4be4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(8)" sheetId="11" r:id="R91f12e6ed14449ba"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(9)" sheetId="12" r:id="Re9a83b007ecf4f93"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(10)" sheetId="13" r:id="R4c3895e5d5a44148"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(11)" sheetId="14" r:id="Raba9b3274b9b4718"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(12)" sheetId="15" r:id="R333892c094594e1a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(13)" sheetId="16" r:id="R7b4d98bbd45742d0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラバムスキル(1)" sheetId="17" r:id="R01827176e325461a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラバムスキル(2)" sheetId="18" r:id="Radec7c10967e4d46"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラバムスキル(3)" sheetId="19" r:id="Rea82872b0935429f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラバムスキル(4)" sheetId="20" r:id="Rd4d78604f8384e5a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(黒精霊の怒り)" sheetId="21" r:id="R8212f835a0cb4f27"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="パッシブ(①)" sheetId="1" r:id="R0810e0de58064f4e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="パッシブ(②)" sheetId="2" r:id="Rf6f1befff44b4972"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(０)" sheetId="3" r:id="R9c0ff8f76e3a49fc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(1)" sheetId="4" r:id="R35f3b751d01e429b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(2)" sheetId="5" r:id="Raa38b22d19d74345"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(3)" sheetId="6" r:id="R68af9376b74f433c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(4)" sheetId="7" r:id="Re5e56b35b40b40c0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(5)" sheetId="8" r:id="Re22d941c88d34396"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(6)" sheetId="9" r:id="R5e3ce152518f4023"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(7)" sheetId="10" r:id="R7413e927fcb54d2b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(8)" sheetId="11" r:id="Rc659038b27014c7c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(9)" sheetId="12" r:id="Rfdcc8854944f41f9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(10)" sheetId="13" r:id="R94e311db10db4c7b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(11)" sheetId="14" r:id="Rc780f802df374b74"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(12)" sheetId="15" r:id="R7a19ca7144ed4160"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(13)" sheetId="16" r:id="Rd2dd7ca101fb4504"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラバムスキル(1)" sheetId="17" r:id="R412ddbd87a464060"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラバムスキル(2)" sheetId="18" r:id="R465cad4d537e418e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラバムスキル(3)" sheetId="19" r:id="R60d953dc4bf64af7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラバムスキル(4)" sheetId="20" r:id="Rcd93f45bb6ce4f33"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(黒精霊の怒り)" sheetId="21" r:id="R6720f874d9c3486f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="プロフィール" sheetId="22" r:id="R7f2e997b6ad148df"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -4267,6 +4268,41 @@
 </x:worksheet>
 </file>
 
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="13.75" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="51.25" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="19.5" customHeight="1">
+      <x:c r="A1" t="str">
+        <x:v>名前</x:v>
+      </x:c>
+      <x:c r="B1" t="str">
+        <x:v>ソンウ・ギョン</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" ht="19.5" customHeight="1">
+      <x:c r="A2" t="str">
+        <x:v>出身地</x:v>
+      </x:c>
+      <x:c r="B2" t="str">
+        <x:v>朝の国・上道房</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="19.5" customHeight="1">
+      <x:c r="A3" t="str">
+        <x:v>Other</x:v>
+      </x:c>
+      <x:c r="B3"/>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="14.25"/>
